--- a/artfynd/A 16438-2024 artfynd.xlsx
+++ b/artfynd/A 16438-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118348268</v>
+        <v>118348043</v>
       </c>
       <c r="B2" t="n">
-        <v>56502</v>
+        <v>78129</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brynjetjärnen (Brynjetjärnen), Jmt</t>
+          <t>Lill-Loken (Lill-Loken), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480006</v>
+        <v>480095</v>
       </c>
       <c r="R2" t="n">
-        <v>6954890</v>
+        <v>6955050</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118348043</v>
+        <v>118348268</v>
       </c>
       <c r="B3" t="n">
-        <v>78129</v>
+        <v>56502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Loken (Lill-Loken), Jmt</t>
+          <t>Brynjetjärnen (Brynjetjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480095</v>
+        <v>480006</v>
       </c>
       <c r="R3" t="n">
-        <v>6955050</v>
+        <v>6954890</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 16438-2024 artfynd.xlsx
+++ b/artfynd/A 16438-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118348043</v>
       </c>
       <c r="B2" t="n">
-        <v>78129</v>
+        <v>78136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 16438-2024 artfynd.xlsx
+++ b/artfynd/A 16438-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118348043</v>
+        <v>118348268</v>
       </c>
       <c r="B2" t="n">
-        <v>78136</v>
+        <v>56502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Loken (Lill-Loken), Jmt</t>
+          <t>Brynjetjärnen (Brynjetjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480095</v>
+        <v>480006</v>
       </c>
       <c r="R2" t="n">
-        <v>6955050</v>
+        <v>6954890</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118348268</v>
+        <v>118348043</v>
       </c>
       <c r="B3" t="n">
-        <v>56502</v>
+        <v>78136</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brynjetjärnen (Brynjetjärnen), Jmt</t>
+          <t>Lill-Loken (Lill-Loken), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480006</v>
+        <v>480095</v>
       </c>
       <c r="R3" t="n">
-        <v>6954890</v>
+        <v>6955050</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
